--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.32223742179552</v>
+        <v>2.814863581041771</v>
       </c>
       <c r="D2" t="n">
-        <v>14.15097169808491</v>
+        <v>2.299532900938797</v>
       </c>
       <c r="E2" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F2" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1769707746155</v>
+        <v>4.741257750875019</v>
       </c>
       <c r="D3" t="n">
-        <v>18.24828759089466</v>
+        <v>2.965346733520382</v>
       </c>
       <c r="E3" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F3" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.19597215062077</v>
+        <v>4.256845474475875</v>
       </c>
       <c r="D4" t="n">
-        <v>36.77635109686658</v>
+        <v>5.97615705324082</v>
       </c>
       <c r="E4" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F4" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.54499813574307</v>
+        <v>3.176062197058249</v>
       </c>
       <c r="D5" t="n">
-        <v>19.29644522428391</v>
+        <v>3.135672348946135</v>
       </c>
       <c r="E5" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F5" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>85.20251051788924</v>
+        <v>13.845407959157</v>
       </c>
       <c r="D6" t="n">
-        <v>84.24668803652841</v>
+        <v>13.69008680593587</v>
       </c>
       <c r="E6" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F6" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.58995717743608</v>
+        <v>6.108368041333363</v>
       </c>
       <c r="D7" t="n">
-        <v>36.62570733657728</v>
+        <v>5.951677442193808</v>
       </c>
       <c r="E7" t="n">
-        <v>23.04183743402164</v>
+        <v>3.744298583028517</v>
       </c>
       <c r="F7" t="n">
-        <v>23.77977603066127</v>
+        <v>3.864213604982456</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
